--- a/etf_holdings/2026-08-21_common_daily_changes_min2_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_min2_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB10"/>
+  <dimension ref="A1:BB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,12 +952,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -1259,12 +1259,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1272,55 +1272,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00403A,00981A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>+0.28%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>142000</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>141,000</t>
-        </is>
-      </c>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -1331,82 +1295,118 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1.59%</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1.81%</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>+0.22%</t>
-        </is>
-      </c>
-      <c r="AP6" t="n">
-        <v>510000</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>550000</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>248000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>257000</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1414,117 +1414,121 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00982A,00991A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>日月光投</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>日月光投</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>1.02%</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>142000</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>141,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="W7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-1,491,000</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1.21%</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>1016000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>959000</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-57,000</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>510000</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>550000</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
@@ -1539,12 +1543,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>日月光投</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1552,121 +1556,117 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00403A,00981A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+          <t>00982A,00991A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4.49%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4.88%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>+0.39%</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>2442000</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2486000</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>44,000</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
+      <c r="V8" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-1,491,000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>3.27%</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>3.63%</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>+0.36%</t>
-        </is>
-      </c>
-      <c r="AP8" t="n">
-        <v>1060000</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>1016000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>959000</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-57,000</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
@@ -1681,12 +1681,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1694,111 +1694,75 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00982A,00991A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+          <t>00981A,00985A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>3.99%</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>4.35%</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>+0.36%</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1.37%</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1.38%</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>450000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>434000</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-16,000</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>833000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>483000</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-350,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
@@ -1809,26 +1773,62 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>-0.73%</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>116000</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>56000</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1836,19 +1836,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00982A,00985A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.49%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2442000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2486000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>44,000</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1859,86 +1895,334 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
-        <v>31000</v>
-      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00982A,00991A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4.35%</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>450000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>434000</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>鴻勁精密</t>
         </is>
       </c>
-      <c r="AV10" t="inlineStr">
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>鴻勁精密</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
         <is>
           <t>1.14%</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1.97%</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>+0.83%</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
         <v>18000</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BA12" t="n">
         <v>31000</v>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>13,000</t>
         </is>

--- a/etf_holdings/2026-08-21_common_daily_changes_min2_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_min2_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:BL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,100 +489,250 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>00991A_異動類型</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>00991A_調整方向</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>00991A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>00991A_權重_今日</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>00991A_權重變化</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>00991A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>00991A_股數_今日</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>00991A_股數變化</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>00980A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>00980A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>00980A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>00980A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>00980A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>00980A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>00980A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>00980A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>00980A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>00980A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>00982A_異動類型</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00982A_調整方向</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>00982A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>00982A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>00982A_權重變化</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>00982A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>00982A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>00982A_股數變化</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00985A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00985A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00985A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00985A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00985A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00985A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00985A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00985A_股數變化</t>
         </is>
@@ -600,11 +750,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00980A,00985A</t>
+          <t>00403A,00980A,00985A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -617,94 +767,160 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>華邦電子</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>華邦電子</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1.70%</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>2.03%</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>+0.33%</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AF2" t="n">
         <v>1942000</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AG2" t="n">
         <v>2293000</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>351,000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-3,000,000</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>華邦電子</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>華邦電子</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.77%</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>0.42%</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="BJ2" t="n">
         <v>447000</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="BK2" t="n">
         <v>243000</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>-204,000</t>
         </is>
@@ -722,11 +938,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00980A,00981A</t>
+          <t>00980A,00981A,00991A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -797,160 +1013,1620 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4.25%</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>-0.64%</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>聯發科技</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>聯發科技</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>4.90%</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>4.62%</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>-0.28%</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="AF3" t="n">
         <v>254000</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AG3" t="n">
         <v>249000</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>-5,000</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00980A,00982A,00991A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4.35%</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>187000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>209000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>450000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>434000</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00403A,00982A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>-0.90%</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>9109000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5285000</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-3,824,000</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>-0.70%</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-10,000,000</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00980A,00982A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>514000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>595000</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>81,000</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>236000</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>688000</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>901000</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>213,000</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>96,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>248000</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>257000</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>142000</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>141,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>510000</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>550000</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00982A,00991A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9000</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-1,491,000</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>1016000</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>959000</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-57,000</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C11" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>00981A,00985A</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0.38%</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.21%</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>-0.17%</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L11" t="n">
         <v>833000</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M11" t="n">
         <v>483000</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>-350,000</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>萬潤科技</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>萬潤科技</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>1.42%</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>0.69%</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>-0.73%</t>
         </is>
       </c>
-      <c r="AF4" t="n">
+      <c r="BJ11" t="n">
         <v>116000</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="BK11" t="n">
         <v>56000</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>-60,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4.49%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2442000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2486000</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>44,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>18000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>31000</v>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>13,000</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-21_common_daily_changes_min2_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_min2_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:BB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,6 +635,56 @@
       <c r="AR1" t="inlineStr">
         <is>
           <t>00982A_股數變化</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
         </is>
       </c>
     </row>
@@ -805,6 +855,16 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -973,16 +1033,26 @@
           <t>-16,000</t>
         </is>
       </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -990,7 +1060,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00980A,00982A</t>
+          <t>00403A,00982A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1013,90 +1083,118 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>1.68%</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>514000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>595000</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>81,000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>-0.90%</t>
+        </is>
+      </c>
       <c r="AP4" t="n">
-        <v>236000</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+        <v>9109000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5285000</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-3,824,000</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>-0.70%</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-10,000,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1104,7 +1202,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00982A,00991A</t>
+          <t>00980A,00982A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1117,102 +1215,662 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>514000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>595000</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>81,000</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>236000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00403A,00980A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1942000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2293000</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>351,000</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-3,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>142000</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>141,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>510000</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>550000</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>日月光投</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00982A,00991A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>日月光投</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>1.02%</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>&lt;0.01%</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
         <v>1500000</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W8" t="n">
         <v>9000</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>-1,491,000</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>日月光投控</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>日月光投控</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1.21%</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>1.14%</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>-0.07%</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AP8" t="n">
         <v>1016000</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ8" t="n">
         <v>959000</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>-57,000</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4.49%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2442000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2486000</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>44,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>40,000</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-21_common_daily_changes_min2_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
+++ b/etf_holdings/2026-08-21_common_daily_changes_min2_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB9"/>
+  <dimension ref="A1:BB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,214 +489,214 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>00991A_異動類型</t>
+          <t>00980A_異動類型</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>00991A_調整方向</t>
+          <t>00980A_調整方向</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>00991A_股票名稱_昨日</t>
+          <t>00980A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>00991A_股票名稱_今日</t>
+          <t>00980A_股票名稱_今日</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>00991A_權重_昨日</t>
+          <t>00980A_權重_昨日</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>00991A_權重_今日</t>
+          <t>00980A_權重_今日</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>00991A_權重變化</t>
+          <t>00980A_權重變化</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>00991A_股數_昨日</t>
+          <t>00980A_股數_昨日</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>00991A_股數_今日</t>
+          <t>00980A_股數_今日</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>00991A_股數變化</t>
+          <t>00980A_股數變化</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>00980A_異動類型</t>
+          <t>00982A_異動類型</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>00980A_調整方向</t>
+          <t>00982A_調整方向</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>00980A_股票名稱_昨日</t>
+          <t>00982A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>00980A_股票名稱_今日</t>
+          <t>00982A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>00980A_權重_昨日</t>
+          <t>00982A_權重_昨日</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>00980A_權重_今日</t>
+          <t>00982A_權重_今日</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>00980A_權重變化</t>
+          <t>00982A_權重變化</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>00980A_股數_昨日</t>
+          <t>00982A_股數_昨日</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>00980A_股數_今日</t>
+          <t>00982A_股數_今日</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>00980A_股數變化</t>
+          <t>00982A_股數變化</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>00982A_異動類型</t>
+          <t>00403A_異動類型</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>00982A_調整方向</t>
+          <t>00403A_調整方向</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>00982A_股票名稱_昨日</t>
+          <t>00403A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>00982A_股票名稱_今日</t>
+          <t>00403A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>00982A_權重_昨日</t>
+          <t>00403A_權重_昨日</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>00982A_權重_今日</t>
+          <t>00403A_權重_今日</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>00982A_權重變化</t>
+          <t>00403A_權重變化</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>00982A_股數_昨日</t>
+          <t>00403A_股數_昨日</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>00982A_股數_今日</t>
+          <t>00403A_股數_今日</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>00982A_股數變化</t>
+          <t>00403A_股數變化</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>00403A_異動類型</t>
+          <t>00985A_異動類型</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>00403A_調整方向</t>
+          <t>00985A_調整方向</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_昨日</t>
+          <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_今日</t>
+          <t>00985A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>00403A_權重_昨日</t>
+          <t>00985A_權重_昨日</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>00403A_權重_今日</t>
+          <t>00985A_權重_今日</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>00403A_權重變化</t>
+          <t>00985A_權重變化</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>00403A_股數_昨日</t>
+          <t>00985A_股數_昨日</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>00403A_股數_今日</t>
+          <t>00985A_股數_今日</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>00403A_股數變化</t>
+          <t>00985A_股數變化</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -704,167 +704,167 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00980A,00981A,00991A</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+          <t>00403A,00980A,00985A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1942000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2293000</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>351,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7.19%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>6.62%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.57%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>5348000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5148000</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-200,000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-3,000,000</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>聯發科技</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>聯發科技</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>4.89%</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>4.25%</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>-0.64%</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>聯發科技</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>聯發科技</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>4.62%</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>-0.28%</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>254000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>249000</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-5,000</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>447000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>243000</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-204,000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00980A,00982A,00991A</t>
+          <t>00403A,00980A,00982A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -917,28 +917,28 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>2300000</v>
+        <v>187000</v>
       </c>
       <c r="W3" t="n">
-        <v>2400000</v>
+        <v>209000</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,55 +948,55 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>434000</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1.44%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1.65%</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>187000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>209000</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>22,000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
           <t>台燿</t>
@@ -1009,28 +1009,28 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>450000</v>
+        <v>1680000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>434000</v>
+        <v>1800000</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-16,000</t>
+          <t>120,000</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
@@ -1083,16 +1083,52 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.87%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>9109000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5285000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-3,824,000</t>
+        </is>
+      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -1115,76 +1151,40 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>9109000</v>
+        <v>70000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5285000</v>
+        <v>60000000</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-3,824,000</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>4.75%</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>-0.70%</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
           <t>-10,000,000</t>
         </is>
       </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1215,88 +1215,88 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>514000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>595000</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>81,000</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>1.68%</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>514000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>595000</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>81,000</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
+        <v>236000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>236000</v>
-      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
@@ -1313,12 +1313,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1326,19 +1326,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00403A,00980A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>00981A,00982A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>294000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-293,000</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -1361,38 +1397,38 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1942000</v>
+        <v>837000</v>
       </c>
       <c r="AG6" t="n">
-        <v>2293000</v>
+        <v>844000</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>351,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr"/>
@@ -1405,62 +1441,26 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1.78%</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1.55%</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-3,000,000</t>
-        </is>
-      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1468,55 +1468,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00403A,00981A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>+0.28%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>142000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>141,000</t>
-        </is>
-      </c>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -1527,16 +1491,52 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>688000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>901000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>213,000</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
@@ -1559,50 +1559,50 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>510000</v>
+        <v>50000</v>
       </c>
       <c r="BA7" t="n">
-        <v>550000</v>
+        <v>146000</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>96,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1610,19 +1610,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00982A,00991A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>00980A,00981A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7.19%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6.92%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5348000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5148000</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -1635,34 +1671,38 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
+          <t>4.62%</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-0.28%</t>
+        </is>
+      </c>
       <c r="V8" t="n">
-        <v>1500000</v>
+        <v>254000</v>
       </c>
       <c r="W8" t="n">
-        <v>9000</v>
+        <v>249000</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-1,491,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1675,52 +1715,16 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1.21%</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="AP8" t="n">
-        <v>1016000</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>959000</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-57,000</t>
-        </is>
-      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
@@ -1735,12 +1739,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1748,55 +1752,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00403A,00981A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4.49%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4.88%</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>+0.39%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>2442000</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2486000</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>44,000</t>
-        </is>
-      </c>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1807,16 +1775,52 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2.96%</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>248000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>257000</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
@@ -1834,43 +1838,593 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AU9" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>142000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>141,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>+0.43%</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>510000</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>610000</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00981A,00985A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>833000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>483000</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-350,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>-0.73%</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>116000</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>56000</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>旺矽</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>旺矽</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4.49%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4.82%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2442000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2486000</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>44,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
         <is>
           <t>3.27%</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3.63%</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>+0.36%</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>3.56%</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
         <v>1060000</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="AQ12" t="n">
         <v>1100000</v>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>40,000</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18000</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>31000</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>13,000</t>
         </is>
       </c>
     </row>
